--- a/docs/templates/mock_drive/2026001 — Rockland/green-sheet/2026001_GREENSHEET.xlsx
+++ b/docs/templates/mock_drive/2026001 — Rockland/green-sheet/2026001_GREENSHEET.xlsx
@@ -918,7 +918,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>selected</t>
+          <t>awarded</t>
         </is>
       </c>
     </row>

--- a/docs/templates/mock_drive/2026001 — Rockland/green-sheet/2026001_GREENSHEET.xlsx
+++ b/docs/templates/mock_drive/2026001 — Rockland/green-sheet/2026001_GREENSHEET.xlsx
@@ -841,7 +841,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>10-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
